--- a/artfynd/A 63779-2021 artfynd.xlsx
+++ b/artfynd/A 63779-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63779-2021 artfynd.xlsx
+++ b/artfynd/A 63779-2021 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>92693515</v>
       </c>
       <c r="B6" t="n">
-        <v>81962</v>
+        <v>83414</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,16 +1204,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kleva, NNO om Mörbylånga, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587004.5635382907</v>
+        <v>587005</v>
       </c>
       <c r="R6" t="n">
-        <v>6268311.893510377</v>
+        <v>6268312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,24 +1245,14 @@
           <t>2021-03-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-03-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3 ex. på naken ved på i marken halvt begravda lövträdsgrenar, (troligen alm eller sälg), under alm, sälg och björk.</t>
+          <t>3 ex. på naken ved på i marken halvt begravda lövträdsgrenar, (troligen alm eller sälg), under alm, sälg och björk. KLURIGA SPORER: Se bilder på hur sporerna snurrar runt och ibland liknar S. coccinea!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1456,7 +1448,7 @@
         <v>92693517</v>
       </c>
       <c r="B8" t="n">
-        <v>81962</v>
+        <v>83414</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1496,16 +1488,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kleva, NNO om Mörbylånga, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586926.8855798536</v>
+        <v>586927</v>
       </c>
       <c r="R8" t="n">
-        <v>6268301.472112998</v>
+        <v>6268301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1535,24 +1529,14 @@
           <t>2021-03-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-03-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4 ex. på naken, svart ved på i marken halvt begravd lövträdsgren, under druvfläder, björk och asp.</t>
+          <t>4 ex. på naken, svart ved på i marken halvt begravd lövträdsgren, under druvfläder, björk och asp. KLURIGA SPORER: Se bilder på hur sporerna snurrar runt och ibland liknar S. coccinea!</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 63779-2021 artfynd.xlsx
+++ b/artfynd/A 63779-2021 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>92693515</v>
       </c>
       <c r="B6" t="n">
-        <v>83414</v>
+        <v>83554</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>92693517</v>
       </c>
       <c r="B8" t="n">
-        <v>83414</v>
+        <v>83554</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 63779-2021 artfynd.xlsx
+++ b/artfynd/A 63779-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97296693</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82964295</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82964079</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82964795</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116967925</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92866328</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82964182</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1604,6 +1644,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82963985</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1711,6 +1756,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124508862</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1833,6 +1883,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116967954</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1954,6 +2009,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124508846</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2054,6 +2114,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora., Ölands Kärlväxtflora</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6455166</t>
         </is>
       </c>
     </row>
@@ -2162,6 +2227,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91172280</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92693515</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2426,6 +2501,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92693516</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2559,8 +2639,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92693517</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>